--- a/docs/Logic Requirements/Ageipelago Genghis Khan.xlsx
+++ b/docs/Logic Requirements/Ageipelago Genghis Khan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE07A875-7858-4D90-98E6-D7911BA92ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0147FCD-88F2-4335-8E72-25DA57D6376B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{A331DE4D-6B47-4A46-A574-F0C6C77C75AD}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{A331DE4D-6B47-4A46-A574-F0C6C77C75AD}"/>
   </bookViews>
   <sheets>
     <sheet name="Genghis Khan" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="216">
   <si>
     <t>Scenario</t>
   </si>
@@ -3455,12 +3455,95 @@
       <t>(not on Standard)</t>
     </r>
   </si>
+  <si>
+    <t>Restrictions</t>
+  </si>
+  <si>
+    <t>Buildings</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Technologies</t>
+  </si>
+  <si>
+    <t>Unavailable</t>
+  </si>
+  <si>
+    <t>Dark Age</t>
+  </si>
+  <si>
+    <t>Dark - Castle Age</t>
+  </si>
+  <si>
+    <t>No Siege Workshop</t>
+  </si>
+  <si>
+    <t>No Battering Ram
+No Mangonel
+No Scorpion
+No Siege Tower
+No Petard</t>
+  </si>
+  <si>
+    <t>Feudal - Imperial Age</t>
+  </si>
+  <si>
+    <t>No Wonder</t>
+  </si>
+  <si>
+    <t>Unrestricted</t>
+  </si>
+  <si>
+    <t>Castle - Imperial Age</t>
+  </si>
+  <si>
+    <t>No Trade Carts</t>
+  </si>
+  <si>
+    <t>No Careening
+No Clinker Construction
+No Siphons
+No Shipwright</t>
+  </si>
+  <si>
+    <t>Imperial Age</t>
+  </si>
+  <si>
+    <t>No Careening
+No Clinker Construction
+No Siphons
+No Carvel Hull
+No Shipwright</t>
+  </si>
+  <si>
+    <t>No Carvel Hull
+No Shipwright
+No Heavy Warships</t>
+  </si>
+  <si>
+    <t>No Fire Ship
+No Fast Fire Ship
+No War Galley
+No Galleon
+No War Hulk
+No Demolition Ship
+No Heavy Demolition Ship
+No Trade Cog
+No Fishing Ship
+No Transport Ship</t>
+  </si>
+  <si>
+    <t>No Dock
+No Fish Trap</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3677,6 +3760,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -3692,7 +3782,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -3865,11 +3955,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4076,6 +4190,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4723,15 +4864,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31308BD0-0CA6-4CE0-9A50-FF6973CEF1CA}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="70" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" s="71"/>
+      <c r="D2" s="72"/>
       <c r="G2" s="2" t="s">
         <v>84</v>
       </c>
@@ -4745,7 +4892,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="73" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="74"/>
+      <c r="D3" s="75"/>
       <c r="G3" s="13" t="s">
         <v>86</v>
       </c>
@@ -4759,7 +4911,16 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>199</v>
+      </c>
       <c r="G4" s="10" t="s">
         <v>121</v>
       </c>
@@ -4773,7 +4934,16 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="76" t="s">
+        <v>200</v>
+      </c>
+      <c r="C5" s="76" t="s">
+        <v>200</v>
+      </c>
+      <c r="D5" s="76" t="s">
+        <v>200</v>
+      </c>
       <c r="G5" s="10" t="s">
         <v>89</v>
       </c>
@@ -4787,7 +4957,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="21"/>
       <c r="G6" s="22" t="s">
         <v>120</v>
       </c>
@@ -4801,7 +4974,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="21"/>
       <c r="G7" s="23" t="s">
         <v>122</v>
       </c>
@@ -4815,7 +4991,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="B8" s="78"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="21"/>
       <c r="G8" s="17" t="s">
         <v>123</v>
       </c>
@@ -4829,7 +5008,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="21"/>
       <c r="G9" s="17" t="s">
         <v>124</v>
       </c>
@@ -4843,7 +5025,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="21"/>
       <c r="G10" s="18" t="s">
         <v>126</v>
       </c>
@@ -4857,7 +5042,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="78"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="21"/>
       <c r="G11" s="18" t="s">
         <v>127</v>
       </c>
@@ -4867,7 +5055,10 @@
       <c r="K11" s="41"/>
       <c r="L11" s="20"/>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="21"/>
       <c r="G12" s="18" t="s">
         <v>111</v>
       </c>
@@ -4877,7 +5068,10 @@
       <c r="K12" s="38"/>
       <c r="L12" s="27"/>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="21"/>
       <c r="G13" s="15" t="s">
         <v>98</v>
       </c>
@@ -4887,7 +5081,10 @@
       <c r="K13" s="38"/>
       <c r="L13" s="27"/>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="78"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="21"/>
       <c r="G14" s="24" t="s">
         <v>128</v>
       </c>
@@ -4897,7 +5094,10 @@
       <c r="K14" s="38"/>
       <c r="L14" s="27"/>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="21"/>
       <c r="G15" s="26" t="s">
         <v>129</v>
       </c>
@@ -4907,7 +5107,10 @@
       <c r="K15" s="38"/>
       <c r="L15" s="27"/>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="77"/>
+      <c r="C16" s="77"/>
+      <c r="D16" s="21"/>
       <c r="G16" s="32"/>
       <c r="H16" s="20"/>
       <c r="K16" s="38"/>
@@ -5070,6 +5273,10 @@
       <c r="L42" s="21"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -5077,15 +5284,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F78F5A24-06D9-4613-ADF6-9B740818E26F}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="70" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" s="71"/>
+      <c r="D2" s="72"/>
       <c r="G2" s="2" t="s">
         <v>84</v>
       </c>
@@ -5099,7 +5312,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="73" t="s">
+        <v>202</v>
+      </c>
+      <c r="C3" s="74"/>
+      <c r="D3" s="75"/>
       <c r="G3" s="13" t="s">
         <v>86</v>
       </c>
@@ -5113,7 +5331,16 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>199</v>
+      </c>
       <c r="G4" s="18" t="s">
         <v>132</v>
       </c>
@@ -5127,7 +5354,16 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="76" t="s">
+        <v>203</v>
+      </c>
+      <c r="C5" s="76" t="s">
+        <v>204</v>
+      </c>
+      <c r="D5" s="76" t="s">
+        <v>210</v>
+      </c>
       <c r="G5" s="59" t="s">
         <v>96</v>
       </c>
@@ -5141,7 +5377,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="21"/>
       <c r="G6" s="18" t="s">
         <v>126</v>
       </c>
@@ -5155,7 +5394,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="21"/>
       <c r="G7" s="18" t="s">
         <v>98</v>
       </c>
@@ -5169,7 +5411,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="78"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="21"/>
       <c r="G8" s="18" t="s">
         <v>94</v>
       </c>
@@ -5183,7 +5428,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="21"/>
       <c r="G9" s="18" t="s">
         <v>92</v>
       </c>
@@ -5197,7 +5445,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="21"/>
       <c r="G10" s="18" t="s">
         <v>133</v>
       </c>
@@ -5211,7 +5462,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="78"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="21"/>
       <c r="G11" s="18" t="s">
         <v>134</v>
       </c>
@@ -5225,7 +5479,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="21"/>
       <c r="G12" s="59" t="s">
         <v>90</v>
       </c>
@@ -5239,7 +5496,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="21"/>
       <c r="G13" s="18" t="s">
         <v>157</v>
       </c>
@@ -5253,7 +5513,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="78"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="21"/>
       <c r="G14" s="42" t="s">
         <v>135</v>
       </c>
@@ -5267,7 +5530,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="21"/>
       <c r="G15" s="16" t="s">
         <v>115</v>
       </c>
@@ -5281,7 +5547,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="77"/>
+      <c r="C16" s="77"/>
+      <c r="D16" s="21"/>
       <c r="G16" s="43" t="s">
         <v>136</v>
       </c>
@@ -5460,21 +5729,31 @@
       <c r="L42" s="21"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F66EF12-2E01-4796-A04D-3CC5263B96D7}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="70" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" s="71"/>
+      <c r="D2" s="72"/>
       <c r="G2" s="2" t="s">
         <v>84</v>
       </c>
@@ -5488,7 +5767,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="73" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3" s="74"/>
+      <c r="D3" s="75"/>
       <c r="G3" s="13" t="s">
         <v>86</v>
       </c>
@@ -5502,7 +5786,16 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>199</v>
+      </c>
       <c r="G4" s="10" t="s">
         <v>121</v>
       </c>
@@ -5516,7 +5809,16 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="76" t="s">
+        <v>206</v>
+      </c>
+      <c r="C5" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="D5" s="76" t="s">
+        <v>207</v>
+      </c>
       <c r="G5" s="10" t="s">
         <v>142</v>
       </c>
@@ -5530,7 +5832,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="21"/>
       <c r="G6" s="22" t="s">
         <v>89</v>
       </c>
@@ -5544,7 +5849,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="21"/>
       <c r="G7" s="47" t="s">
         <v>132</v>
       </c>
@@ -5558,7 +5866,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="78"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="21"/>
       <c r="G8" s="60" t="s">
         <v>113</v>
       </c>
@@ -5572,7 +5883,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="21"/>
       <c r="G9" s="47" t="s">
         <v>92</v>
       </c>
@@ -5586,7 +5900,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="21"/>
       <c r="G10" s="18" t="s">
         <v>127</v>
       </c>
@@ -5600,7 +5917,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="78"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="21"/>
       <c r="G11" s="18" t="s">
         <v>94</v>
       </c>
@@ -5614,7 +5934,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="21"/>
       <c r="G12" s="59" t="s">
         <v>143</v>
       </c>
@@ -5628,7 +5951,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="21"/>
       <c r="G13" s="18" t="s">
         <v>111</v>
       </c>
@@ -5642,7 +5968,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="78"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="21"/>
       <c r="G14" s="59" t="s">
         <v>144</v>
       </c>
@@ -5656,7 +5985,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="21"/>
       <c r="G15" s="18" t="s">
         <v>145</v>
       </c>
@@ -5670,7 +6002,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="77"/>
+      <c r="C16" s="77"/>
+      <c r="D16" s="21"/>
       <c r="G16" s="18" t="s">
         <v>103</v>
       </c>
@@ -5965,21 +6300,31 @@
       <c r="L42" s="21"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{092F5795-A134-4210-B2B0-D916144240D9}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="70" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" s="71"/>
+      <c r="D2" s="72"/>
       <c r="G2" s="2" t="s">
         <v>84</v>
       </c>
@@ -5993,7 +6338,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="73" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" s="74"/>
+      <c r="D3" s="75"/>
       <c r="G3" s="13" t="s">
         <v>86</v>
       </c>
@@ -6007,7 +6357,16 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>199</v>
+      </c>
       <c r="G4" s="10" t="s">
         <v>142</v>
       </c>
@@ -6021,7 +6380,16 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="C5" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="D5" s="76" t="s">
+        <v>207</v>
+      </c>
       <c r="G5" s="10" t="s">
         <v>121</v>
       </c>
@@ -6035,7 +6403,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="21"/>
       <c r="G6" s="10" t="s">
         <v>89</v>
       </c>
@@ -6049,7 +6420,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="21"/>
       <c r="G7" s="10" t="s">
         <v>120</v>
       </c>
@@ -6063,7 +6437,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="78"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="21"/>
       <c r="G8" s="58" t="s">
         <v>166</v>
       </c>
@@ -6077,7 +6454,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="21"/>
       <c r="G9" s="16" t="s">
         <v>126</v>
       </c>
@@ -6091,7 +6471,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="21"/>
       <c r="G10" s="16" t="s">
         <v>133</v>
       </c>
@@ -6105,7 +6488,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="78"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="21"/>
       <c r="G11" s="18" t="s">
         <v>132</v>
       </c>
@@ -6119,7 +6505,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="21"/>
       <c r="G12" s="18" t="s">
         <v>98</v>
       </c>
@@ -6133,7 +6522,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="21"/>
       <c r="G13" s="18" t="s">
         <v>109</v>
       </c>
@@ -6147,7 +6539,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="78"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="21"/>
       <c r="G14" s="59" t="s">
         <v>167</v>
       </c>
@@ -6161,7 +6556,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="21"/>
       <c r="G15" s="18" t="s">
         <v>157</v>
       </c>
@@ -6175,7 +6573,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="77"/>
+      <c r="C16" s="77"/>
+      <c r="D16" s="21"/>
       <c r="G16" s="18" t="s">
         <v>145</v>
       </c>
@@ -6420,21 +6821,31 @@
       <c r="L42" s="21"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06F03CB9-C806-4868-9E11-49F2A0DE8B6D}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="70" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" s="71"/>
+      <c r="D2" s="72"/>
       <c r="G2" s="2" t="s">
         <v>84</v>
       </c>
@@ -6448,7 +6859,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="73" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" s="74"/>
+      <c r="D3" s="75"/>
       <c r="G3" s="7" t="s">
         <v>86</v>
       </c>
@@ -6462,7 +6878,16 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>199</v>
+      </c>
       <c r="G4" s="52" t="s">
         <v>132</v>
       </c>
@@ -6476,7 +6901,16 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" ht="113.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="C5" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="D5" s="76" t="s">
+        <v>212</v>
+      </c>
       <c r="G5" s="52" t="s">
         <v>109</v>
       </c>
@@ -6490,7 +6924,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="21"/>
       <c r="G6" s="64" t="s">
         <v>176</v>
       </c>
@@ -6504,7 +6941,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="21"/>
       <c r="G7" s="52" t="s">
         <v>177</v>
       </c>
@@ -6518,7 +6958,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="78"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="21"/>
       <c r="G8" s="52" t="s">
         <v>157</v>
       </c>
@@ -6532,7 +6975,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="21"/>
       <c r="G9" s="52" t="s">
         <v>158</v>
       </c>
@@ -6546,7 +6992,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="21"/>
       <c r="G10" s="52" t="s">
         <v>159</v>
       </c>
@@ -6560,7 +7009,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="78"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="21"/>
       <c r="G11" s="52" t="s">
         <v>195</v>
       </c>
@@ -6574,7 +7026,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="21"/>
       <c r="G12" s="53" t="s">
         <v>94</v>
       </c>
@@ -6588,7 +7043,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="21"/>
       <c r="G13" s="53" t="s">
         <v>92</v>
       </c>
@@ -6602,7 +7060,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="78"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="21"/>
       <c r="G14" s="53" t="s">
         <v>145</v>
       </c>
@@ -6616,7 +7077,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="21"/>
       <c r="G15" s="53" t="s">
         <v>103</v>
       </c>
@@ -6630,7 +7094,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="77"/>
+      <c r="C16" s="77"/>
+      <c r="D16" s="21"/>
       <c r="G16" s="66" t="s">
         <v>178</v>
       </c>
@@ -6877,21 +7344,31 @@
       <c r="L42" s="21"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72983E84-249F-406E-9E63-A9ACF895D43B}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="70" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" s="71"/>
+      <c r="D2" s="72"/>
       <c r="G2" s="2" t="s">
         <v>84</v>
       </c>
@@ -6905,7 +7382,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="73" t="s">
+        <v>211</v>
+      </c>
+      <c r="C3" s="74"/>
+      <c r="D3" s="75"/>
       <c r="G3" s="13" t="s">
         <v>86</v>
       </c>
@@ -6919,7 +7401,16 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>199</v>
+      </c>
       <c r="G4" s="13" t="s">
         <v>121</v>
       </c>
@@ -6933,7 +7424,16 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" ht="207" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="C5" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="D5" s="76" t="s">
+        <v>213</v>
+      </c>
       <c r="G5" s="55" t="s">
         <v>92</v>
       </c>
@@ -6947,7 +7447,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="21"/>
       <c r="G6" s="55" t="s">
         <v>177</v>
       </c>
@@ -6961,7 +7464,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="21"/>
       <c r="G7" s="67" t="s">
         <v>190</v>
       </c>
@@ -6975,7 +7481,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="78"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="21"/>
       <c r="G8" s="55" t="s">
         <v>103</v>
       </c>
@@ -6989,7 +7498,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="21"/>
       <c r="G9" s="55" t="s">
         <v>147</v>
       </c>
@@ -7003,7 +7515,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="21"/>
       <c r="G10" s="55" t="s">
         <v>107</v>
       </c>
@@ -7017,7 +7532,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="78"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="21"/>
       <c r="G11" s="55" t="s">
         <v>98</v>
       </c>
@@ -7031,7 +7549,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="21"/>
       <c r="G12" s="55" t="s">
         <v>132</v>
       </c>
@@ -7045,7 +7566,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="21"/>
       <c r="G13" s="67" t="s">
         <v>191</v>
       </c>
@@ -7059,7 +7583,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="78"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="21"/>
       <c r="G14" s="55" t="s">
         <v>182</v>
       </c>
@@ -7073,7 +7600,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="21"/>
       <c r="G15" s="55" t="s">
         <v>134</v>
       </c>
@@ -7087,7 +7617,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="77"/>
+      <c r="C16" s="77"/>
+      <c r="D16" s="21"/>
       <c r="G16" s="67" t="s">
         <v>192</v>
       </c>
@@ -7282,6 +7815,10 @@
       <c r="L42" s="21"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/Logic Requirements/Ageipelago Genghis Khan.xlsx
+++ b/docs/Logic Requirements/Ageipelago Genghis Khan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0147FCD-88F2-4335-8E72-25DA57D6376B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFA8846-B577-4300-8923-BF0C91E7EBFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{A331DE4D-6B47-4A46-A574-F0C6C77C75AD}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A331DE4D-6B47-4A46-A574-F0C6C77C75AD}"/>
   </bookViews>
   <sheets>
     <sheet name="Genghis Khan" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="213">
   <si>
     <t>Scenario</t>
   </si>
@@ -414,95 +414,6 @@
         <family val="2"/>
       </rPr>
       <t>Engineers</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Destroy </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>1/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2/3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Castle/s
-Destroy </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>1 Wonder</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Jin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> before they start building a Wonder
-Find the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Siege Workshops</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> in China</t>
     </r>
   </si>
   <si>
@@ -790,11 +701,6 @@
 200 Stone</t>
   </si>
   <si>
-    <t>10 Elite Leiciai
-1 Monk
-1 Monestary</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Build 3 Castles in the flagged Area
 Defend against </t>
@@ -1086,72 +992,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Defeating </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Jin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> quickly is a Steam Achievement, but I'm not a Fan of this one personally.
-The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Tanguts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tribute 10k of each Resource to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Jin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> as soon as the Player optains the Villagers, making them a much greater Threat.</t>
-    </r>
-  </si>
-  <si>
     <t>One more Speedrun Achievement, once more, not a Fan.
 Maybe keeping the Bridge from being destroyed would be a good Item? Not much to work with here for a final Scenario…</t>
   </si>
@@ -1389,96 +1229,6 @@
         <family val="2"/>
       </rPr>
       <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Bring 2/3 Relic/s to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>the Ungirrad Monestary</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Ungirrad</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Kereyids</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF30F2FC"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Uighurs</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Kara-Khitai</t>
     </r>
   </si>
   <si>
@@ -3026,16 +2776,6 @@
     <t>Ornlu the Wolf</t>
   </si>
   <si>
-    <t>Elite Mangudai</t>
-  </si>
-  <si>
-    <t>Genghis Khan</t>
-  </si>
-  <si>
-    <t>No items required
-Disappears after Intro</t>
-  </si>
-  <si>
     <t>Cavalry Archer</t>
   </si>
   <si>
@@ -3538,24 +3278,276 @@
     <t>No Dock
 No Fish Trap</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bring 2/3 Relic/s to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">the Ungirrad Monestary
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Bring 30/40 Sheep to the Kereyids</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ungirrad</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Kereyids</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF30F2FC"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Uighurs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Kara-Khitai</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Destroy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2/3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Castle/s
+Destroy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1 Wonder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Jin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> before they start building a Wonder
+Reach the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Bombard Cannons</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in China
+Reach the Villagers
+Reach the Transport Ship</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Defeating </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Jin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> before they start building a Wonder is a Steam Achievement, but I'm not a Fan of this one personally.
+The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tanguts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tribute 10k of each Resource to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Jin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as soon as the Player optains the Villagers, making them a much greater Threat.</t>
+    </r>
+  </si>
+  <si>
+    <t>10 Elite Leiciai, 1 Monk, 1 Monestary</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="24"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="18"/>
@@ -3569,12 +3561,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color rgb="FF3A3A3A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
@@ -3611,13 +3597,6 @@
     <font>
       <sz val="14"/>
       <color rgb="FFFFFF00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color rgb="FF3A3A3A"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3763,6 +3742,28 @@
     <font>
       <sz val="24"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3983,69 +3984,150 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4054,169 +4136,76 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4541,7 +4530,7 @@
   <dimension ref="B2:Q9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="28.85546875" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="74" customWidth="1"/>
     <col min="3" max="3" width="26.85546875" customWidth="1"/>
     <col min="4" max="4" width="29.42578125" customWidth="1"/>
     <col min="5" max="5" width="33.42578125" customWidth="1"/>
@@ -4561,300 +4550,300 @@
   <sheetData>
     <row r="2" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:17" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="N3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="O3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="P3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="Q3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="O3" s="4" t="s">
+    </row>
+    <row r="4" spans="2:17" ht="319.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="73" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N4" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="O4" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="P4" s="6" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="4" spans="2:17" ht="319.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="Q4" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="8"/>
+      <c r="I5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="K5" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7" t="s">
+      <c r="L5" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q4" s="8" t="s">
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="10"/>
-      <c r="I5" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="8" t="s">
+    <row r="6" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="76" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="M6" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="N6" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="10" t="s">
+    </row>
+    <row r="7" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="J6" s="8" t="s">
+      <c r="H7" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="394.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="I8" s="9"/>
+      <c r="J8" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="K8" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K6" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="K7" s="8" t="s">
+      <c r="L8" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="L7" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8" t="s">
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="394.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="9" t="s">
+    <row r="9" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="73" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="10" t="s">
+      <c r="E9" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="K8" s="8" t="s">
+      <c r="G9" s="8"/>
+      <c r="H9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="L8" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -4874,403 +4863,386 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="70" t="s">
-        <v>196</v>
-      </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="72"/>
-      <c r="G2" s="2" t="s">
+      <c r="B2" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" s="65"/>
+      <c r="D2" s="66"/>
+      <c r="G2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="68"/>
+      <c r="D3" s="69"/>
+      <c r="G3" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K2" s="2" t="s">
+      <c r="L3" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="61" t="s">
+        <v>193</v>
+      </c>
+      <c r="C5" s="61" t="s">
+        <v>193</v>
+      </c>
+      <c r="D5" s="61" t="s">
+        <v>193</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="73" t="s">
-        <v>201</v>
-      </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="75"/>
-      <c r="G3" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="H3" s="9" t="s">
+      <c r="H5" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="18"/>
+      <c r="G6" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="K3" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G4" s="10" t="s">
+      <c r="L6" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="18"/>
+      <c r="G7" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="18"/>
+      <c r="G8" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="62"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="18"/>
+      <c r="G9" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="62"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="18"/>
+      <c r="G10" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="70" t="s">
+        <v>98</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="18"/>
+      <c r="G11" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="L11" s="17"/>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="18"/>
+      <c r="G12" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K4" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="76" t="s">
-        <v>200</v>
-      </c>
-      <c r="C5" s="76" t="s">
-        <v>200</v>
-      </c>
-      <c r="D5" s="76" t="s">
-        <v>200</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K5" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="77"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="21"/>
-      <c r="G6" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="77"/>
-      <c r="C7" s="77"/>
-      <c r="D7" s="21"/>
-      <c r="G7" s="23" t="s">
+      <c r="H12" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="L12" s="24"/>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="18"/>
+      <c r="G13" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="H7" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K7" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="B8" s="78"/>
-      <c r="C8" s="78"/>
-      <c r="D8" s="21"/>
-      <c r="G8" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="K8" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="B9" s="77"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="21"/>
-      <c r="G9" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="K9" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="21"/>
-      <c r="G10" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K10" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="L10" s="19" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="21"/>
-      <c r="G11" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K11" s="41"/>
-      <c r="L11" s="20"/>
-    </row>
-    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="21"/>
-      <c r="G12" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K12" s="38"/>
-      <c r="L12" s="27"/>
-    </row>
-    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="77"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="21"/>
-      <c r="G13" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K13" s="38"/>
-      <c r="L13" s="27"/>
+      <c r="H13" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L13" s="24"/>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="21"/>
-      <c r="G14" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K14" s="38"/>
-      <c r="L14" s="27"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="18"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="72"/>
+      <c r="L14" s="24"/>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="77"/>
-      <c r="C15" s="77"/>
-      <c r="D15" s="21"/>
-      <c r="G15" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="H15" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="K15" s="38"/>
-      <c r="L15" s="27"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="18"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="L15" s="24"/>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="77"/>
-      <c r="C16" s="77"/>
-      <c r="D16" s="21"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="20"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="27"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="18"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="24"/>
+      <c r="L16" s="24"/>
     </row>
     <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="28"/>
-      <c r="H17" s="27"/>
-      <c r="K17" s="39"/>
-      <c r="L17" s="27"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="24"/>
+      <c r="L17" s="24"/>
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="29"/>
-      <c r="H18" s="27"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="27"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="24"/>
+      <c r="L18" s="24"/>
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="30"/>
-      <c r="H19" s="27"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="24"/>
+      <c r="L19" s="24"/>
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="29"/>
-      <c r="H20" s="27"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="27"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="24"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="24"/>
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="31"/>
-      <c r="H21" s="27"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="27"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="24"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="24"/>
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="31"/>
-      <c r="H22" s="27"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="27"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="24"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="24"/>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="31"/>
-      <c r="H23" s="27"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="27"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="24"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="24"/>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="27"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
-      <c r="K27" s="21"/>
-      <c r="L27" s="21"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
     </row>
     <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="K32" s="21"/>
-      <c r="L32" s="21"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="21"/>
-      <c r="H34" s="21"/>
-      <c r="K34" s="21"/>
-      <c r="L34" s="21"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
     </row>
     <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-      <c r="K35" s="21"/>
-      <c r="L35" s="21"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="21"/>
-      <c r="H37" s="21"/>
-      <c r="K37" s="21"/>
-      <c r="L37" s="21"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
     </row>
     <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-      <c r="K38" s="21"/>
-      <c r="L38" s="21"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
     </row>
     <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
     </row>
     <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="21"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
     </row>
     <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-      <c r="K41" s="21"/>
-      <c r="L41" s="21"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
     </row>
     <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-      <c r="K42" s="21"/>
-      <c r="L42" s="21"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5294,439 +5266,443 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" s="65"/>
+      <c r="D2" s="66"/>
+      <c r="G2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="67" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" s="68"/>
+      <c r="D3" s="69"/>
+      <c r="G3" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="61" t="s">
         <v>196</v>
       </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="72"/>
-      <c r="G2" s="2" t="s">
+      <c r="C5" s="61" t="s">
+        <v>197</v>
+      </c>
+      <c r="D5" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="G5" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="18"/>
+      <c r="G6" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="18"/>
+      <c r="G7" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="18"/>
+      <c r="G8" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="62"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="18"/>
+      <c r="G9" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="62"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="18"/>
+      <c r="G10" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="18"/>
+      <c r="G11" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="18"/>
+      <c r="G12" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="18"/>
+      <c r="G13" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="73" t="s">
-        <v>202</v>
-      </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="75"/>
-      <c r="G3" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K3" s="33" t="s">
-        <v>130</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K4" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="76" t="s">
-        <v>203</v>
-      </c>
-      <c r="C5" s="76" t="s">
-        <v>204</v>
-      </c>
-      <c r="D5" s="76" t="s">
-        <v>210</v>
-      </c>
-      <c r="G5" s="59" t="s">
-        <v>96</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K5" s="34" t="s">
-        <v>137</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="77"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="21"/>
-      <c r="G6" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="34" t="s">
+      <c r="L13" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="18"/>
+      <c r="G14" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="L6" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="77"/>
-      <c r="C7" s="77"/>
-      <c r="D7" s="21"/>
-      <c r="G7" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K7" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="78"/>
-      <c r="C8" s="78"/>
-      <c r="D8" s="21"/>
-      <c r="G8" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K8" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="77"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="21"/>
-      <c r="G9" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K9" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="21"/>
-      <c r="G10" s="18" t="s">
+      <c r="L14" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="18"/>
+      <c r="G15" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K10" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="21"/>
-      <c r="G11" s="18" t="s">
+      <c r="L15" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="62"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="18"/>
+      <c r="G16" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="29"/>
+      <c r="H17" s="17"/>
+      <c r="K17" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G18" s="26"/>
+      <c r="H18" s="24"/>
+      <c r="K18" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K11" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="21"/>
-      <c r="G12" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K12" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="77"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="21"/>
-      <c r="G13" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K13" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="21"/>
-      <c r="G14" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K14" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="77"/>
-      <c r="C15" s="77"/>
-      <c r="D15" s="21"/>
-      <c r="G15" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K15" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="77"/>
-      <c r="C16" s="77"/>
-      <c r="D16" s="21"/>
-      <c r="G16" s="43" t="s">
-        <v>136</v>
-      </c>
-      <c r="H16" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="K16" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="32"/>
-      <c r="H17" s="20"/>
-      <c r="K17" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G18" s="29"/>
-      <c r="H18" s="27"/>
-      <c r="K18" s="43" t="s">
-        <v>141</v>
-      </c>
-      <c r="L18" s="19" t="s">
-        <v>87</v>
+      <c r="L18" s="16" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="30"/>
-      <c r="H19" s="27"/>
-      <c r="K19" s="45"/>
-      <c r="L19" s="20"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="24"/>
+      <c r="K19" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="29"/>
-      <c r="H20" s="27"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="27"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="24"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="24"/>
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="31"/>
-      <c r="H21" s="27"/>
-      <c r="K21" s="44"/>
-      <c r="L21" s="27"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="24"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="24"/>
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="31"/>
-      <c r="H22" s="27"/>
-      <c r="K22" s="44"/>
-      <c r="L22" s="27"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="24"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="24"/>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="31"/>
-      <c r="H23" s="27"/>
-      <c r="K23" s="44"/>
-      <c r="L23" s="27"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="24"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="24"/>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="27"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
-      <c r="K27" s="21"/>
-      <c r="L27" s="21"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
     </row>
     <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="K32" s="21"/>
-      <c r="L32" s="21"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="21"/>
-      <c r="H34" s="21"/>
-      <c r="K34" s="21"/>
-      <c r="L34" s="21"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
     </row>
     <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-      <c r="K35" s="21"/>
-      <c r="L35" s="21"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="21"/>
-      <c r="H37" s="21"/>
-      <c r="K37" s="21"/>
-      <c r="L37" s="21"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
     </row>
     <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-      <c r="K38" s="21"/>
-      <c r="L38" s="21"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
     </row>
     <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
     </row>
     <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="21"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
     </row>
     <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-      <c r="K41" s="21"/>
-      <c r="L41" s="21"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
     </row>
     <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-      <c r="K42" s="21"/>
-      <c r="L42" s="21"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5749,555 +5725,555 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="70" t="s">
-        <v>196</v>
-      </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="72"/>
-      <c r="G2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K2" s="2" t="s">
+      <c r="B2" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" s="65"/>
+      <c r="D2" s="66"/>
+      <c r="G2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="67" t="s">
+        <v>198</v>
+      </c>
+      <c r="C3" s="68"/>
+      <c r="D3" s="69"/>
+      <c r="G3" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="61" t="s">
+        <v>199</v>
+      </c>
+      <c r="C5" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="D5" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="18"/>
+      <c r="G6" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="73" t="s">
-        <v>205</v>
-      </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="75"/>
-      <c r="G3" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="H3" s="9" t="s">
+      <c r="H6" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="18"/>
+      <c r="G7" s="38" t="s">
+        <v>125</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="18"/>
+      <c r="G8" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="59" t="s">
+        <v>156</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="62"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="18"/>
+      <c r="G9" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="62"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="18"/>
+      <c r="G10" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="18"/>
+      <c r="G11" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="18"/>
+      <c r="G12" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="K3" s="49" t="s">
+      <c r="L12" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="18"/>
+      <c r="G13" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="18"/>
+      <c r="G14" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="18"/>
+      <c r="G15" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="62"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="18"/>
+      <c r="G16" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="L3" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K4" s="50" t="s">
-        <v>162</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="76" t="s">
-        <v>206</v>
-      </c>
-      <c r="C5" s="76" t="s">
-        <v>207</v>
-      </c>
-      <c r="D5" s="76" t="s">
-        <v>207</v>
-      </c>
-      <c r="G5" s="10" t="s">
+      <c r="H16" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G18" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G19" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K22" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K23" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="52" t="s">
+        <v>141</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="52" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K5" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="77"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="21"/>
-      <c r="G6" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="50" t="s">
-        <v>95</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="77"/>
-      <c r="C7" s="77"/>
-      <c r="D7" s="21"/>
-      <c r="G7" s="47" t="s">
-        <v>132</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K7" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="78"/>
-      <c r="C8" s="78"/>
-      <c r="D8" s="21"/>
-      <c r="G8" s="60" t="s">
-        <v>113</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K8" s="68" t="s">
-        <v>163</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="77"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="21"/>
-      <c r="G9" s="47" t="s">
-        <v>92</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K9" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="21"/>
-      <c r="G10" s="18" t="s">
+      <c r="H25" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="K27" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+    </row>
+    <row r="29" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G29" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
+    </row>
+    <row r="30" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G30" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
+    </row>
+    <row r="31" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G31" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
+    </row>
+    <row r="32" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G32" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="54" t="s">
+        <v>149</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K10" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="21"/>
-      <c r="G11" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K11" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="21"/>
-      <c r="G12" s="59" t="s">
-        <v>143</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K12" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="77"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="21"/>
-      <c r="G13" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K13" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="21"/>
-      <c r="G14" s="59" t="s">
-        <v>144</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K14" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="77"/>
-      <c r="C15" s="77"/>
-      <c r="D15" s="21"/>
-      <c r="G15" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K15" s="34" t="s">
-        <v>137</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="77"/>
-      <c r="C16" s="77"/>
-      <c r="D16" s="21"/>
-      <c r="G16" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K16" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K17" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G18" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K18" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="G19" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K19" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K20" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="43" t="s">
-        <v>115</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K21" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="43" t="s">
-        <v>147</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K22" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K23" s="43" t="s">
-        <v>110</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="61" t="s">
-        <v>148</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K24" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="L24" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="61" t="s">
-        <v>149</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K25" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="17" t="s">
+      <c r="H34" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="H26" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="K26" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="L26" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="62" t="s">
-        <v>105</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="K27" s="48" t="s">
-        <v>165</v>
-      </c>
-      <c r="L27" s="19" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="62" t="s">
+      <c r="H35" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+    </row>
+    <row r="36" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G36" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="H28" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-    </row>
-    <row r="29" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G29" s="17" t="s">
+      <c r="H36" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="H29" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-    </row>
-    <row r="30" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G30" s="62" t="s">
-        <v>153</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-    </row>
-    <row r="31" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G31" s="62" t="s">
-        <v>154</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
-    </row>
-    <row r="32" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G32" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="K32" s="21"/>
-      <c r="L32" s="21"/>
-    </row>
-    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="63" t="s">
-        <v>156</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
-    </row>
-    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K34" s="21"/>
-      <c r="L34" s="21"/>
-    </row>
-    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K35" s="21"/>
-      <c r="L35" s="21"/>
-    </row>
-    <row r="36" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G36" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
-    </row>
-    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K37" s="21"/>
-      <c r="L37" s="21"/>
+      <c r="H37" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
     </row>
     <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K38" s="21"/>
-      <c r="L38" s="21"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
     </row>
     <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
     </row>
     <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="21"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
     </row>
     <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-      <c r="K41" s="21"/>
-      <c r="L41" s="21"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
     </row>
     <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-      <c r="K42" s="21"/>
-      <c r="L42" s="21"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6320,505 +6296,505 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="70" t="s">
-        <v>196</v>
-      </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="72"/>
-      <c r="G2" s="2" t="s">
+      <c r="B2" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" s="65"/>
+      <c r="D2" s="66"/>
+      <c r="G2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="67" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="68"/>
+      <c r="D3" s="69"/>
+      <c r="G3" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="C5" s="61" t="s">
+        <v>202</v>
+      </c>
+      <c r="D5" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="18"/>
+      <c r="G6" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="18"/>
+      <c r="G7" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="18"/>
+      <c r="G8" s="49" t="s">
+        <v>159</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="62"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="18"/>
+      <c r="G9" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="62"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="18"/>
+      <c r="G10" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="18"/>
+      <c r="G11" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="18"/>
+      <c r="G12" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="18"/>
+      <c r="G13" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="18"/>
+      <c r="G14" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="18"/>
+      <c r="G15" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="62"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="18"/>
+      <c r="G16" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="73" t="s">
-        <v>208</v>
-      </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="75"/>
-      <c r="G3" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="H3" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="K3" s="51" t="s">
-        <v>130</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K4" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="76" t="s">
-        <v>207</v>
-      </c>
-      <c r="C5" s="76" t="s">
-        <v>209</v>
-      </c>
-      <c r="D5" s="76" t="s">
-        <v>207</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K5" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="77"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="21"/>
-      <c r="G6" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="77"/>
-      <c r="C7" s="77"/>
-      <c r="D7" s="21"/>
-      <c r="G7" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K7" s="16" t="s">
+      <c r="L16" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="L7" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="78"/>
-      <c r="C8" s="78"/>
-      <c r="D8" s="21"/>
-      <c r="G8" s="58" t="s">
+      <c r="L17" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G19" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G23" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="H8" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K8" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="77"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="21"/>
-      <c r="G9" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="21"/>
-      <c r="G10" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K10" s="18" t="s">
+      <c r="H23" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K23" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="L10" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="21"/>
-      <c r="G11" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K11" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="21"/>
-      <c r="G12" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K12" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="77"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="21"/>
-      <c r="G13" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K13" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="21"/>
-      <c r="G14" s="59" t="s">
+      <c r="L23" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G24" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K25" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="H14" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K14" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="77"/>
-      <c r="C15" s="77"/>
-      <c r="D15" s="21"/>
-      <c r="G15" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K15" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="77"/>
-      <c r="C16" s="77"/>
-      <c r="D16" s="21"/>
-      <c r="G16" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K16" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K17" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K18" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G19" s="17" t="s">
+      <c r="L25" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="K26" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="H19" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K19" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K20" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K21" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K22" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G23" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K23" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G24" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K24" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="L24" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K25" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="K26" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="L26" s="9" t="s">
-        <v>87</v>
+      <c r="L26" s="7" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
-      <c r="K27" s="48" t="s">
-        <v>165</v>
-      </c>
-      <c r="L27" s="19" t="s">
-        <v>87</v>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="K27" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="K30" s="27"/>
-      <c r="L30" s="27"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="24"/>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
     </row>
     <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="K32" s="21"/>
-      <c r="L32" s="21"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="21"/>
-      <c r="H34" s="21"/>
-      <c r="K34" s="21"/>
-      <c r="L34" s="21"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
     </row>
     <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-      <c r="K35" s="21"/>
-      <c r="L35" s="21"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="21"/>
-      <c r="H37" s="21"/>
-      <c r="K37" s="21"/>
-      <c r="L37" s="21"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
     </row>
     <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-      <c r="K38" s="21"/>
-      <c r="L38" s="21"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
     </row>
     <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
     </row>
     <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="21"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
     </row>
     <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-      <c r="K41" s="21"/>
-      <c r="L41" s="21"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
     </row>
     <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-      <c r="K42" s="21"/>
-      <c r="L42" s="21"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6841,507 +6817,507 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="70" t="s">
-        <v>196</v>
-      </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="72"/>
-      <c r="G2" s="2" t="s">
+      <c r="B2" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" s="65"/>
+      <c r="D2" s="66"/>
+      <c r="G2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="67" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="68"/>
+      <c r="D3" s="69"/>
+      <c r="G3" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G4" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="43" t="s">
+        <v>155</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="113.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="C5" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="D5" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="G5" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="18"/>
+      <c r="G6" s="55" t="s">
+        <v>169</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="18"/>
+      <c r="G7" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="18"/>
+      <c r="G8" s="43" t="s">
+        <v>150</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="62"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="18"/>
+      <c r="G9" s="43" t="s">
+        <v>151</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="62"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="18"/>
+      <c r="G10" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="18"/>
+      <c r="G11" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="43" t="s">
+        <v>95</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="18"/>
+      <c r="G12" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="18"/>
+      <c r="G13" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="18"/>
+      <c r="G14" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="18"/>
+      <c r="G15" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="73" t="s">
-        <v>208</v>
-      </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="75"/>
-      <c r="G3" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="H3" s="7" t="s">
+      <c r="L15" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="62"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="18"/>
+      <c r="G16" s="57" t="s">
+        <v>171</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="L16" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G17" s="57" t="s">
+        <v>172</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="L17" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G18" s="57" t="s">
+        <v>173</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K18" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="L18" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G19" s="57" t="s">
+        <v>174</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K19" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G20" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K20" s="57" t="s">
+        <v>178</v>
+      </c>
+      <c r="L20" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G21" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K21" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="L21" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G22" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K22" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="K3" s="52" t="s">
-        <v>138</v>
-      </c>
-      <c r="L3" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G4" s="52" t="s">
-        <v>132</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K4" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="L4" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="113.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="76" t="s">
-        <v>207</v>
-      </c>
-      <c r="C5" s="76" t="s">
-        <v>207</v>
-      </c>
-      <c r="D5" s="76" t="s">
-        <v>212</v>
-      </c>
-      <c r="G5" s="52" t="s">
-        <v>109</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K5" s="52" t="s">
-        <v>117</v>
-      </c>
-      <c r="L5" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="77"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="21"/>
-      <c r="G6" s="64" t="s">
+      <c r="L22" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G23" s="56" t="s">
         <v>176</v>
       </c>
-      <c r="H6" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="52" t="s">
-        <v>101</v>
-      </c>
-      <c r="L6" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="77"/>
-      <c r="C7" s="77"/>
-      <c r="D7" s="21"/>
-      <c r="G7" s="52" t="s">
-        <v>177</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K7" s="52" t="s">
-        <v>100</v>
-      </c>
-      <c r="L7" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="78"/>
-      <c r="C8" s="78"/>
-      <c r="D8" s="21"/>
-      <c r="G8" s="52" t="s">
-        <v>157</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K8" s="52" t="s">
-        <v>102</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="77"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="21"/>
-      <c r="G9" s="52" t="s">
-        <v>158</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K9" s="52" t="s">
-        <v>139</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="21"/>
-      <c r="G10" s="52" t="s">
-        <v>159</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K10" s="52" t="s">
-        <v>118</v>
-      </c>
-      <c r="L10" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="21"/>
-      <c r="G11" s="52" t="s">
-        <v>195</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K11" s="52" t="s">
-        <v>99</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="21"/>
-      <c r="G12" s="53" t="s">
-        <v>94</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K12" s="52" t="s">
-        <v>137</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="77"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="21"/>
-      <c r="G13" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K13" s="52" t="s">
-        <v>95</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="21"/>
-      <c r="G14" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K14" s="52" t="s">
-        <v>106</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="77"/>
-      <c r="C15" s="77"/>
-      <c r="D15" s="21"/>
-      <c r="G15" s="53" t="s">
-        <v>103</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K15" s="52" t="s">
-        <v>88</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="77"/>
-      <c r="C16" s="77"/>
-      <c r="D16" s="21"/>
-      <c r="G16" s="66" t="s">
-        <v>178</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K16" s="64" t="s">
-        <v>184</v>
-      </c>
-      <c r="L16" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G17" s="66" t="s">
+      <c r="H23" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K23" s="42" t="s">
         <v>179</v>
       </c>
-      <c r="H17" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K17" s="52" t="s">
-        <v>164</v>
-      </c>
-      <c r="L17" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="18" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G18" s="66" t="s">
+      <c r="L23" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G24" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K24" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="L24" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="K25" s="60" t="s">
         <v>180</v>
       </c>
-      <c r="H18" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K18" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="L18" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" spans="7:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G19" s="66" t="s">
+      <c r="L25" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="K26" s="60" t="s">
         <v>181</v>
       </c>
-      <c r="H19" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K19" s="53" t="s">
-        <v>116</v>
-      </c>
-      <c r="L19" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G20" s="51" t="s">
+      <c r="L26" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="K27" s="60" t="s">
         <v>182</v>
       </c>
-      <c r="H20" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K20" s="66" t="s">
-        <v>185</v>
-      </c>
-      <c r="L20" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G21" s="54" t="s">
-        <v>107</v>
-      </c>
-      <c r="H21" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K21" s="53" t="s">
-        <v>97</v>
-      </c>
-      <c r="L21" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G22" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K22" s="53" t="s">
-        <v>91</v>
-      </c>
-      <c r="L22" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G23" s="65" t="s">
-        <v>183</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K23" s="51" t="s">
-        <v>186</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G24" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K24" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="L24" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="K25" s="69" t="s">
-        <v>187</v>
-      </c>
-      <c r="L25" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="26" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="K26" s="69" t="s">
-        <v>188</v>
-      </c>
-      <c r="L26" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
-      <c r="K27" s="69" t="s">
-        <v>189</v>
-      </c>
-      <c r="L27" s="13" t="s">
-        <v>87</v>
+      <c r="L27" s="10" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
     </row>
     <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="K32" s="21"/>
-      <c r="L32" s="21"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="21"/>
-      <c r="H34" s="21"/>
-      <c r="K34" s="21"/>
-      <c r="L34" s="21"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
     </row>
     <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-      <c r="K35" s="21"/>
-      <c r="L35" s="21"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="21"/>
-      <c r="H37" s="21"/>
-      <c r="K37" s="21"/>
-      <c r="L37" s="21"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
     </row>
     <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-      <c r="K38" s="21"/>
-      <c r="L38" s="21"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
     </row>
     <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
     </row>
     <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="21"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
     </row>
     <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-      <c r="K41" s="21"/>
-      <c r="L41" s="21"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
     </row>
     <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-      <c r="K42" s="21"/>
-      <c r="L42" s="21"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7364,455 +7340,455 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="70" t="s">
-        <v>196</v>
-      </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="72"/>
-      <c r="G2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>55</v>
+      <c r="B2" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" s="65"/>
+      <c r="D2" s="66"/>
+      <c r="G2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="73" t="s">
-        <v>211</v>
-      </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="75"/>
-      <c r="G3" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="H3" s="13" t="s">
+      <c r="B3" s="67" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3" s="68"/>
+      <c r="D3" s="69"/>
+      <c r="G3" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="46" t="s">
+        <v>179</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="207" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="61" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" s="61" t="s">
+        <v>207</v>
+      </c>
+      <c r="D5" s="61" t="s">
+        <v>206</v>
+      </c>
+      <c r="G5" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="18"/>
+      <c r="G6" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="18"/>
+      <c r="G7" s="58" t="s">
+        <v>183</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="18"/>
+      <c r="G8" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="K3" s="55" t="s">
-        <v>118</v>
-      </c>
-      <c r="L3" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K4" s="55" t="s">
-        <v>186</v>
-      </c>
-      <c r="L4" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="207" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="76" t="s">
-        <v>215</v>
-      </c>
-      <c r="C5" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="D5" s="76" t="s">
-        <v>213</v>
-      </c>
-      <c r="G5" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K5" s="55" t="s">
-        <v>117</v>
-      </c>
-      <c r="L5" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="77"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="21"/>
-      <c r="G6" s="55" t="s">
-        <v>177</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="55" t="s">
-        <v>138</v>
-      </c>
-      <c r="L6" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="77"/>
-      <c r="C7" s="77"/>
-      <c r="D7" s="21"/>
-      <c r="G7" s="67" t="s">
-        <v>190</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K7" s="55" t="s">
-        <v>162</v>
-      </c>
-      <c r="L7" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="78"/>
-      <c r="C8" s="78"/>
-      <c r="D8" s="21"/>
-      <c r="G8" s="55" t="s">
+      <c r="L8" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="62"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="18"/>
+      <c r="G9" s="46" t="s">
+        <v>140</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="62"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="18"/>
+      <c r="G10" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="H8" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K8" s="55" t="s">
+      <c r="H10" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="18"/>
+      <c r="G11" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="18"/>
+      <c r="G12" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="18"/>
+      <c r="G13" s="58" t="s">
+        <v>184</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" s="46" t="s">
+        <v>110</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="18"/>
+      <c r="G14" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" s="46" t="s">
+        <v>112</v>
+      </c>
+      <c r="L14" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="18"/>
+      <c r="G15" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="62"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="18"/>
+      <c r="G16" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="L16" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="K17" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="L17" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="K18" s="58" t="s">
+        <v>100</v>
+      </c>
+      <c r="L18" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="K19" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="K20" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="L20" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="K21" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="L8" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="77"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="21"/>
-      <c r="G9" s="55" t="s">
-        <v>147</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K9" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="21"/>
-      <c r="G10" s="55" t="s">
-        <v>107</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K10" s="55" t="s">
-        <v>100</v>
-      </c>
-      <c r="L10" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="21"/>
-      <c r="G11" s="55" t="s">
-        <v>98</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K11" s="55" t="s">
-        <v>99</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="21"/>
-      <c r="G12" s="55" t="s">
-        <v>132</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K12" s="55" t="s">
-        <v>106</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="77"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="21"/>
-      <c r="G13" s="67" t="s">
-        <v>191</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K13" s="55" t="s">
-        <v>114</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="21"/>
-      <c r="G14" s="55" t="s">
-        <v>182</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K14" s="55" t="s">
-        <v>116</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="77"/>
-      <c r="C15" s="77"/>
-      <c r="D15" s="21"/>
-      <c r="G15" s="55" t="s">
-        <v>134</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K15" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="77"/>
-      <c r="C16" s="77"/>
-      <c r="D16" s="21"/>
-      <c r="G16" s="67" t="s">
-        <v>192</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K16" s="55" t="s">
-        <v>164</v>
-      </c>
-      <c r="L16" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="K17" s="55" t="s">
-        <v>139</v>
-      </c>
-      <c r="L17" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="18" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="K18" s="67" t="s">
-        <v>104</v>
-      </c>
-      <c r="L18" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="K19" s="55" t="s">
-        <v>137</v>
-      </c>
-      <c r="L19" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="K20" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="L20" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="K21" s="55" t="s">
-        <v>95</v>
-      </c>
-      <c r="L21" s="13" t="s">
-        <v>87</v>
+      <c r="L21" s="10" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="K22" s="56" t="s">
-        <v>165</v>
-      </c>
-      <c r="L22" s="57" t="s">
-        <v>87</v>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="K22" s="47" t="s">
+        <v>158</v>
+      </c>
+      <c r="L22" s="48" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="27"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
-      <c r="K27" s="21"/>
-      <c r="L27" s="21"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
     </row>
     <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
     </row>
     <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="K32" s="21"/>
-      <c r="L32" s="21"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="21"/>
-      <c r="H34" s="21"/>
-      <c r="K34" s="21"/>
-      <c r="L34" s="21"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
     </row>
     <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-      <c r="K35" s="21"/>
-      <c r="L35" s="21"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="21"/>
-      <c r="H37" s="21"/>
-      <c r="K37" s="21"/>
-      <c r="L37" s="21"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
     </row>
     <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-      <c r="K38" s="21"/>
-      <c r="L38" s="21"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
     </row>
     <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
     </row>
     <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="21"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
     </row>
     <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-      <c r="K41" s="21"/>
-      <c r="L41" s="21"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
     </row>
     <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-      <c r="K42" s="21"/>
-      <c r="L42" s="21"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/docs/Logic Requirements/Ageipelago Genghis Khan.xlsx
+++ b/docs/Logic Requirements/Ageipelago Genghis Khan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFA8846-B577-4300-8923-BF0C91E7EBFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD3A490-C010-41D6-B827-CA7325DE9887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A331DE4D-6B47-4A46-A574-F0C6C77C75AD}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{A331DE4D-6B47-4A46-A574-F0C6C77C75AD}"/>
   </bookViews>
   <sheets>
     <sheet name="Genghis Khan" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="225">
   <si>
     <t>Scenario</t>
   </si>
@@ -3535,6 +3535,42 @@
   </si>
   <si>
     <t>10 Elite Leiciai, 1 Monk, 1 Monestary</t>
+  </si>
+  <si>
+    <t>Starting Units</t>
+  </si>
+  <si>
+    <t>Starting Buildings</t>
+  </si>
+  <si>
+    <t>Item-Units</t>
+  </si>
+  <si>
+    <t>Item-Buildings</t>
+  </si>
+  <si>
+    <t>Transport Ship</t>
+  </si>
+  <si>
+    <t>Bombard Cannon</t>
+  </si>
+  <si>
+    <t>Trade Cart</t>
+  </si>
+  <si>
+    <t>Hunting Wolf</t>
+  </si>
+  <si>
+    <t>Subotai</t>
+  </si>
+  <si>
+    <t>Elite Leitis</t>
+  </si>
+  <si>
+    <t>Saboteur</t>
+  </si>
+  <si>
+    <t>Khan</t>
   </si>
 </sst>
 </file>
@@ -3783,7 +3819,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -3980,11 +4016,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4172,7 +4219,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4193,19 +4252,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4530,7 +4586,7 @@
   <dimension ref="B2:Q9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="28.85546875" style="74" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="67" customWidth="1"/>
     <col min="3" max="3" width="26.85546875" customWidth="1"/>
     <col min="4" max="4" width="29.42578125" customWidth="1"/>
     <col min="5" max="5" width="33.42578125" customWidth="1"/>
@@ -4550,7 +4606,7 @@
   <sheetData>
     <row r="2" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:17" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="68" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -4600,7 +4656,7 @@
       </c>
     </row>
     <row r="4" spans="2:17" ht="319.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="73" t="s">
+      <c r="B4" s="66" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -4646,7 +4702,7 @@
       </c>
     </row>
     <row r="5" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="73" t="s">
+      <c r="B5" s="66" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="7" t="s">
@@ -4686,7 +4742,7 @@
       </c>
     </row>
     <row r="6" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="76" t="s">
+      <c r="B6" s="69" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="7" t="s">
@@ -4732,7 +4788,7 @@
       </c>
     </row>
     <row r="7" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="73" t="s">
+      <c r="B7" s="66" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="7" t="s">
@@ -4774,7 +4830,7 @@
       </c>
     </row>
     <row r="8" spans="2:17" ht="394.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="73" t="s">
+      <c r="B8" s="66" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="7" t="s">
@@ -4812,7 +4868,7 @@
       </c>
     </row>
     <row r="9" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="73" t="s">
+      <c r="B9" s="66" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="7" t="s">
@@ -4857,17 +4913,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="70" t="s">
         <v>189</v>
       </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="66"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="72"/>
       <c r="G2" s="1" t="s">
         <v>80</v>
       </c>
@@ -4882,11 +4939,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="73" t="s">
         <v>194</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="69"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="75"/>
       <c r="G3" s="10" t="s">
         <v>82</v>
       </c>
@@ -4963,7 +5020,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="62"/>
       <c r="C7" s="62"/>
       <c r="D7" s="18"/>
@@ -4980,10 +5037,19 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="18"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="G8" s="15" t="s">
         <v>119</v>
       </c>
@@ -4998,9 +5064,12 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="62"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="18"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="79" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="36"/>
       <c r="G9" s="15" t="s">
         <v>120</v>
       </c>
@@ -5015,16 +5084,19 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="18"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="61" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" s="36"/>
       <c r="G10" s="15" t="s">
         <v>107</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="K10" s="70" t="s">
+      <c r="K10" s="63" t="s">
         <v>98</v>
       </c>
       <c r="L10" s="16" t="s">
@@ -5032,9 +5104,12 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="63"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="18"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" s="36"/>
       <c r="G11" s="12" t="s">
         <v>94</v>
       </c>
@@ -5044,9 +5119,12 @@
       <c r="L11" s="17"/>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="62"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="18"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="79" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" s="36"/>
       <c r="G12" s="21" t="s">
         <v>121</v>
       </c>
@@ -5056,9 +5134,12 @@
       <c r="L12" s="24"/>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="62"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="18"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="78" t="s">
+        <v>119</v>
+      </c>
+      <c r="E13" s="36"/>
       <c r="G13" s="23" t="s">
         <v>122</v>
       </c>
@@ -5068,117 +5149,146 @@
       <c r="L13" s="24"/>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="63"/>
-      <c r="C14" s="63"/>
-      <c r="D14" s="18"/>
-      <c r="G14" s="72"/>
-      <c r="H14" s="72"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="61" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="36"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
       <c r="L14" s="24"/>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="62"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="18"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="61" t="s">
+        <v>121</v>
+      </c>
+      <c r="E15" s="36"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="64"/>
       <c r="L15" s="24"/>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="62"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="18"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="61" t="s">
+        <v>122</v>
+      </c>
+      <c r="E16" s="36"/>
       <c r="G16" s="25"/>
       <c r="H16" s="24"/>
       <c r="L16" s="24"/>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
       <c r="G17" s="25"/>
       <c r="H17" s="24"/>
       <c r="L17" s="24"/>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
       <c r="G18" s="26"/>
       <c r="H18" s="24"/>
       <c r="L18" s="24"/>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
       <c r="G19" s="27"/>
       <c r="H19" s="24"/>
       <c r="L19" s="24"/>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
       <c r="G20" s="26"/>
       <c r="H20" s="24"/>
       <c r="K20" s="33"/>
       <c r="L20" s="24"/>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
       <c r="G21" s="28"/>
       <c r="H21" s="24"/>
       <c r="K21" s="33"/>
       <c r="L21" s="24"/>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="28"/>
       <c r="H22" s="24"/>
       <c r="K22" s="25"/>
       <c r="L22" s="24"/>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="28"/>
       <c r="H23" s="24"/>
       <c r="K23" s="25"/>
       <c r="L23" s="24"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="24"/>
       <c r="H24" s="24"/>
       <c r="K24" s="24"/>
       <c r="L24" s="24"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="18"/>
       <c r="H25" s="18"/>
       <c r="K25" s="18"/>
       <c r="L25" s="18"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="18"/>
       <c r="H26" s="18"/>
       <c r="K26" s="18"/>
       <c r="L26" s="18"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="18"/>
       <c r="H27" s="18"/>
       <c r="K27" s="18"/>
       <c r="L27" s="18"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="18"/>
       <c r="H28" s="18"/>
       <c r="K28" s="18"/>
       <c r="L28" s="18"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="18"/>
       <c r="H29" s="18"/>
       <c r="K29" s="18"/>
       <c r="L29" s="18"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="18"/>
       <c r="H30" s="18"/>
       <c r="K30" s="18"/>
       <c r="L30" s="18"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="18"/>
       <c r="H31" s="18"/>
       <c r="K31" s="18"/>
       <c r="L31" s="18"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="18"/>
       <c r="H32" s="18"/>
       <c r="K32" s="18"/>
@@ -5260,17 +5370,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="70" t="s">
         <v>189</v>
       </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="66"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="72"/>
       <c r="G2" s="1" t="s">
         <v>80</v>
       </c>
@@ -5285,11 +5396,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="73" t="s">
         <v>195</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="69"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="75"/>
       <c r="G3" s="10" t="s">
         <v>82</v>
       </c>
@@ -5366,7 +5477,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="62"/>
       <c r="C7" s="62"/>
       <c r="D7" s="18"/>
@@ -5383,10 +5494,19 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="18"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="G8" s="15" t="s">
         <v>90</v>
       </c>
@@ -5401,9 +5521,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="62"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="18"/>
+      <c r="B9" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="36"/>
+      <c r="D9" s="76" t="s">
+        <v>125</v>
+      </c>
+      <c r="E9" s="61" t="s">
+        <v>131</v>
+      </c>
       <c r="G9" s="15" t="s">
         <v>88</v>
       </c>
@@ -5418,9 +5545,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="18"/>
+      <c r="B10" s="61" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="19" t="s">
+        <v>97</v>
+      </c>
       <c r="G10" s="15" t="s">
         <v>126</v>
       </c>
@@ -5435,9 +5567,12 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="63"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="18"/>
+      <c r="B11" s="61" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
       <c r="G11" s="15" t="s">
         <v>127</v>
       </c>
@@ -5452,9 +5587,10 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="62"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="18"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
       <c r="G12" s="50" t="s">
         <v>86</v>
       </c>
@@ -5469,9 +5605,10 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="62"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="18"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
       <c r="G13" s="15" t="s">
         <v>150</v>
       </c>
@@ -5486,9 +5623,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="63"/>
-      <c r="C14" s="63"/>
-      <c r="D14" s="18"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
       <c r="G14" s="34" t="s">
         <v>128</v>
       </c>
@@ -5503,9 +5641,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="62"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="18"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
       <c r="G15" s="13" t="s">
         <v>111</v>
       </c>
@@ -5520,9 +5659,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="62"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="18"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
       <c r="G16" s="35" t="s">
         <v>129</v>
       </c>
@@ -5536,7 +5676,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
       <c r="G17" s="29"/>
       <c r="H17" s="17"/>
       <c r="K17" s="13" t="s">
@@ -5546,7 +5690,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
       <c r="G18" s="26"/>
       <c r="H18" s="24"/>
       <c r="K18" s="35" t="s">
@@ -5556,7 +5704,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
       <c r="G19" s="27"/>
       <c r="H19" s="24"/>
       <c r="K19" s="13" t="s">
@@ -5566,79 +5718,87 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
       <c r="G20" s="26"/>
       <c r="H20" s="24"/>
       <c r="K20" s="36"/>
       <c r="L20" s="24"/>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
       <c r="G21" s="28"/>
       <c r="H21" s="24"/>
       <c r="K21" s="36"/>
       <c r="L21" s="24"/>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="28"/>
       <c r="H22" s="24"/>
       <c r="K22" s="36"/>
       <c r="L22" s="24"/>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="28"/>
       <c r="H23" s="24"/>
       <c r="K23" s="36"/>
       <c r="L23" s="24"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="24"/>
       <c r="H24" s="24"/>
       <c r="K24" s="24"/>
       <c r="L24" s="24"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="18"/>
       <c r="H25" s="18"/>
       <c r="K25" s="18"/>
       <c r="L25" s="18"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="18"/>
       <c r="H26" s="18"/>
       <c r="K26" s="18"/>
       <c r="L26" s="18"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="18"/>
       <c r="H27" s="18"/>
       <c r="K27" s="18"/>
       <c r="L27" s="18"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="18"/>
       <c r="H28" s="18"/>
       <c r="K28" s="18"/>
       <c r="L28" s="18"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="18"/>
       <c r="H29" s="18"/>
       <c r="K29" s="18"/>
       <c r="L29" s="18"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="18"/>
       <c r="H30" s="18"/>
       <c r="K30" s="18"/>
       <c r="L30" s="18"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="18"/>
       <c r="H31" s="18"/>
       <c r="K31" s="18"/>
       <c r="L31" s="18"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="18"/>
       <c r="H32" s="18"/>
       <c r="K32" s="18"/>
@@ -5719,17 +5879,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="70" t="s">
         <v>189</v>
       </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="66"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="72"/>
       <c r="G2" s="1" t="s">
         <v>80</v>
       </c>
@@ -5744,11 +5905,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="73" t="s">
         <v>198</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="69"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="75"/>
       <c r="G3" s="10" t="s">
         <v>82</v>
       </c>
@@ -5825,7 +5986,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="62"/>
       <c r="C7" s="62"/>
       <c r="D7" s="18"/>
@@ -5842,10 +6003,19 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="18"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="G8" s="51" t="s">
         <v>109</v>
       </c>
@@ -5860,9 +6030,14 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="62"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="18"/>
+      <c r="B9" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="36"/>
+      <c r="D9" s="61" t="s">
+        <v>217</v>
+      </c>
+      <c r="E9" s="36"/>
       <c r="G9" s="38" t="s">
         <v>88</v>
       </c>
@@ -5877,9 +6052,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="18"/>
+      <c r="B10" s="61" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="36"/>
+      <c r="D10" s="79" t="s">
+        <v>218</v>
+      </c>
+      <c r="E10" s="36"/>
       <c r="G10" s="15" t="s">
         <v>120</v>
       </c>
@@ -5894,9 +6074,12 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="63"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="18"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="78" t="s">
+        <v>125</v>
+      </c>
+      <c r="E11" s="36"/>
       <c r="G11" s="15" t="s">
         <v>90</v>
       </c>
@@ -5911,9 +6094,12 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="62"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="18"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="E12" s="36"/>
       <c r="G12" s="50" t="s">
         <v>136</v>
       </c>
@@ -5928,9 +6114,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="62"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="18"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="61" t="s">
+        <v>120</v>
+      </c>
+      <c r="E13" s="36"/>
       <c r="G13" s="15" t="s">
         <v>107</v>
       </c>
@@ -5945,9 +6134,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="63"/>
-      <c r="C14" s="63"/>
-      <c r="D14" s="18"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
       <c r="G14" s="50" t="s">
         <v>137</v>
       </c>
@@ -5962,9 +6152,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="62"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="18"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
       <c r="G15" s="15" t="s">
         <v>138</v>
       </c>
@@ -5979,9 +6170,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="62"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="18"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
       <c r="G16" s="15" t="s">
         <v>99</v>
       </c>
@@ -5995,7 +6187,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
       <c r="G17" s="15" t="s">
         <v>139</v>
       </c>
@@ -6009,7 +6205,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
       <c r="G18" s="20" t="s">
         <v>186</v>
       </c>
@@ -6023,7 +6223,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
       <c r="G19" s="19" t="s">
         <v>187</v>
       </c>
@@ -6037,7 +6241,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
       <c r="G20" s="13" t="s">
         <v>94</v>
       </c>
@@ -6051,7 +6259,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
       <c r="G21" s="35" t="s">
         <v>111</v>
       </c>
@@ -6065,7 +6277,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="35" t="s">
         <v>140</v>
       </c>
@@ -6079,7 +6291,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="13" t="s">
         <v>103</v>
       </c>
@@ -6093,7 +6305,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="52" t="s">
         <v>141</v>
       </c>
@@ -6107,7 +6319,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="52" t="s">
         <v>142</v>
       </c>
@@ -6121,7 +6333,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="14" t="s">
         <v>143</v>
       </c>
@@ -6135,7 +6347,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="53" t="s">
         <v>101</v>
       </c>
@@ -6149,7 +6361,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="53" t="s">
         <v>144</v>
       </c>
@@ -6159,7 +6371,7 @@
       <c r="K28" s="17"/>
       <c r="L28" s="17"/>
     </row>
-    <row r="29" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G29" s="14" t="s">
         <v>145</v>
       </c>
@@ -6169,7 +6381,7 @@
       <c r="K29" s="18"/>
       <c r="L29" s="18"/>
     </row>
-    <row r="30" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G30" s="53" t="s">
         <v>146</v>
       </c>
@@ -6179,7 +6391,7 @@
       <c r="K30" s="18"/>
       <c r="L30" s="18"/>
     </row>
-    <row r="31" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G31" s="53" t="s">
         <v>147</v>
       </c>
@@ -6189,7 +6401,7 @@
       <c r="K31" s="18"/>
       <c r="L31" s="18"/>
     </row>
-    <row r="32" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G32" s="14" t="s">
         <v>148</v>
       </c>
@@ -6290,17 +6502,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="70" t="s">
         <v>189</v>
       </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="66"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="72"/>
       <c r="G2" s="1" t="s">
         <v>80</v>
       </c>
@@ -6315,11 +6528,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="73" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="69"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="75"/>
       <c r="G3" s="10" t="s">
         <v>82</v>
       </c>
@@ -6396,7 +6609,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="62"/>
       <c r="C7" s="62"/>
       <c r="D7" s="18"/>
@@ -6413,10 +6626,19 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="18"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="G8" s="49" t="s">
         <v>159</v>
       </c>
@@ -6431,9 +6653,18 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="62"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="18"/>
+      <c r="B9" s="61" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" s="76" t="s">
+        <v>152</v>
+      </c>
+      <c r="E9" s="79" t="s">
+        <v>93</v>
+      </c>
       <c r="G9" s="13" t="s">
         <v>119</v>
       </c>
@@ -6448,9 +6679,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="18"/>
+      <c r="B10" s="61" t="s">
+        <v>219</v>
+      </c>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="79" t="s">
+        <v>130</v>
+      </c>
       <c r="G10" s="13" t="s">
         <v>126</v>
       </c>
@@ -6465,9 +6701,14 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="63"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="18"/>
+      <c r="B11" s="61" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="79" t="s">
+        <v>87</v>
+      </c>
       <c r="G11" s="15" t="s">
         <v>125</v>
       </c>
@@ -6482,9 +6723,14 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="62"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="18"/>
+      <c r="B12" s="61" t="s">
+        <v>220</v>
+      </c>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="79" t="s">
+        <v>100</v>
+      </c>
       <c r="G12" s="15" t="s">
         <v>94</v>
       </c>
@@ -6499,9 +6745,14 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="62"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="18"/>
+      <c r="B13" s="61" t="s">
+        <v>221</v>
+      </c>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="61" t="s">
+        <v>102</v>
+      </c>
       <c r="G13" s="15" t="s">
         <v>105</v>
       </c>
@@ -6516,9 +6767,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="63"/>
-      <c r="C14" s="63"/>
-      <c r="D14" s="18"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
       <c r="G14" s="50" t="s">
         <v>160</v>
       </c>
@@ -6533,9 +6785,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="62"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="18"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
       <c r="G15" s="15" t="s">
         <v>150</v>
       </c>
@@ -6550,9 +6803,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="62"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="18"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
       <c r="G16" s="15" t="s">
         <v>138</v>
       </c>
@@ -6566,7 +6820,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
       <c r="G17" s="11" t="s">
         <v>88</v>
       </c>
@@ -6580,7 +6838,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
       <c r="G18" s="11" t="s">
         <v>122</v>
       </c>
@@ -6594,7 +6856,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
       <c r="G19" s="14" t="s">
         <v>161</v>
       </c>
@@ -6608,7 +6874,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
       <c r="G20" s="14" t="s">
         <v>162</v>
       </c>
@@ -6622,7 +6892,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
       <c r="G21" s="11" t="s">
         <v>107</v>
       </c>
@@ -6636,7 +6910,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="14" t="s">
         <v>163</v>
       </c>
@@ -6650,7 +6924,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G23" s="11" t="s">
         <v>166</v>
       </c>
@@ -6664,7 +6938,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G24" s="11" t="s">
         <v>165</v>
       </c>
@@ -6678,7 +6952,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="K25" s="11" t="s">
         <v>167</v>
       </c>
@@ -6686,7 +6960,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="18"/>
       <c r="H26" s="18"/>
       <c r="K26" s="14" t="s">
@@ -6696,7 +6970,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="18"/>
       <c r="H27" s="18"/>
       <c r="K27" s="39" t="s">
@@ -6706,31 +6980,31 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="18"/>
       <c r="H28" s="18"/>
       <c r="K28" s="17"/>
       <c r="L28" s="17"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="18"/>
       <c r="H29" s="18"/>
       <c r="K29" s="24"/>
       <c r="L29" s="24"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="18"/>
       <c r="H30" s="18"/>
       <c r="K30" s="24"/>
       <c r="L30" s="24"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="18"/>
       <c r="H31" s="18"/>
       <c r="K31" s="18"/>
       <c r="L31" s="18"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="18"/>
       <c r="H32" s="18"/>
       <c r="K32" s="18"/>
@@ -6811,17 +7085,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="70" t="s">
         <v>189</v>
       </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="66"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="72"/>
       <c r="G2" s="1" t="s">
         <v>80</v>
       </c>
@@ -6836,11 +7111,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="73" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="69"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="75"/>
       <c r="G3" s="5" t="s">
         <v>82</v>
       </c>
@@ -6934,10 +7209,19 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="18"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="G8" s="43" t="s">
         <v>150</v>
       </c>
@@ -6952,9 +7236,18 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="62"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="18"/>
+      <c r="B9" s="61" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="76" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" s="79" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9" s="77" t="s">
+        <v>100</v>
+      </c>
       <c r="G9" s="43" t="s">
         <v>151</v>
       </c>
@@ -6969,9 +7262,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="18"/>
+      <c r="B10" s="61" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="36"/>
+      <c r="D10" s="61" t="s">
+        <v>222</v>
+      </c>
+      <c r="E10" s="36"/>
       <c r="G10" s="43" t="s">
         <v>152</v>
       </c>
@@ -6986,9 +7284,12 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="63"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="18"/>
+      <c r="B11" s="61" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
       <c r="G11" s="43" t="s">
         <v>188</v>
       </c>
@@ -7003,9 +7304,10 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="62"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="18"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
       <c r="G12" s="44" t="s">
         <v>90</v>
       </c>
@@ -7020,9 +7322,10 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="62"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="18"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
       <c r="G13" s="44" t="s">
         <v>88</v>
       </c>
@@ -7037,9 +7340,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="63"/>
-      <c r="C14" s="63"/>
-      <c r="D14" s="18"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
       <c r="G14" s="44" t="s">
         <v>138</v>
       </c>
@@ -7054,9 +7358,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="62"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="18"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
       <c r="G15" s="44" t="s">
         <v>99</v>
       </c>
@@ -7071,9 +7376,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="62"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="18"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
       <c r="G16" s="57" t="s">
         <v>171</v>
       </c>
@@ -7087,7 +7393,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
       <c r="G17" s="57" t="s">
         <v>172</v>
       </c>
@@ -7101,7 +7411,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
       <c r="G18" s="57" t="s">
         <v>173</v>
       </c>
@@ -7115,7 +7429,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
       <c r="G19" s="57" t="s">
         <v>174</v>
       </c>
@@ -7129,7 +7447,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
       <c r="G20" s="42" t="s">
         <v>175</v>
       </c>
@@ -7143,7 +7465,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
       <c r="G21" s="45" t="s">
         <v>103</v>
       </c>
@@ -7157,7 +7483,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G22" s="34" t="s">
         <v>139</v>
       </c>
@@ -7171,7 +7497,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G23" s="56" t="s">
         <v>176</v>
       </c>
@@ -7185,7 +7511,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G24" s="42" t="s">
         <v>107</v>
       </c>
@@ -7199,7 +7525,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G25" s="18"/>
       <c r="H25" s="18"/>
       <c r="K25" s="60" t="s">
@@ -7209,7 +7535,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G26" s="18"/>
       <c r="H26" s="18"/>
       <c r="K26" s="60" t="s">
@@ -7219,7 +7545,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="18"/>
       <c r="H27" s="18"/>
       <c r="K27" s="60" t="s">
@@ -7229,31 +7555,31 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="18"/>
       <c r="H28" s="18"/>
       <c r="K28" s="18"/>
       <c r="L28" s="18"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="18"/>
       <c r="H29" s="18"/>
       <c r="K29" s="18"/>
       <c r="L29" s="18"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="18"/>
       <c r="H30" s="18"/>
       <c r="K30" s="18"/>
       <c r="L30" s="18"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="18"/>
       <c r="H31" s="18"/>
       <c r="K31" s="18"/>
       <c r="L31" s="18"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="18"/>
       <c r="H32" s="18"/>
       <c r="K32" s="18"/>
@@ -7334,17 +7660,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="70" t="s">
         <v>189</v>
       </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="66"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="72"/>
       <c r="G2" s="1" t="s">
         <v>80</v>
       </c>
@@ -7359,11 +7686,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="73" t="s">
         <v>204</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="69"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="75"/>
       <c r="G3" s="10" t="s">
         <v>82</v>
       </c>
@@ -7457,10 +7784,19 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="18"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="G8" s="46" t="s">
         <v>99</v>
       </c>
@@ -7475,9 +7811,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="62"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="18"/>
+      <c r="B9" s="61" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="76" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" s="79" t="s">
+        <v>221</v>
+      </c>
+      <c r="E9" s="36"/>
       <c r="G9" s="46" t="s">
         <v>140</v>
       </c>
@@ -7492,9 +7835,16 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="18"/>
+      <c r="B10" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="76" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="79" t="s">
+        <v>220</v>
+      </c>
+      <c r="E10" s="36"/>
       <c r="G10" s="46" t="s">
         <v>103</v>
       </c>
@@ -7509,9 +7859,16 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="63"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="18"/>
+      <c r="B11" s="61" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="76" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" s="61" t="s">
+        <v>224</v>
+      </c>
+      <c r="E11" s="36"/>
       <c r="G11" s="46" t="s">
         <v>94</v>
       </c>
@@ -7526,9 +7883,14 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="62"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="18"/>
+      <c r="B12" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
       <c r="G12" s="46" t="s">
         <v>125</v>
       </c>
@@ -7543,9 +7905,10 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="62"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="18"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
       <c r="G13" s="58" t="s">
         <v>184</v>
       </c>
@@ -7560,9 +7923,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="63"/>
-      <c r="C14" s="63"/>
-      <c r="D14" s="18"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
       <c r="G14" s="46" t="s">
         <v>175</v>
       </c>
@@ -7577,9 +7941,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="62"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="18"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
       <c r="G15" s="46" t="s">
         <v>127</v>
       </c>
@@ -7594,9 +7959,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="62"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="18"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
       <c r="G16" s="58" t="s">
         <v>185</v>
       </c>
@@ -7610,7 +7976,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
       <c r="G17" s="24"/>
       <c r="H17" s="24"/>
       <c r="K17" s="46" t="s">
@@ -7620,7 +7990,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
       <c r="G18" s="24"/>
       <c r="H18" s="24"/>
       <c r="K18" s="58" t="s">
@@ -7630,7 +8004,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
       <c r="G19" s="24"/>
       <c r="H19" s="24"/>
       <c r="K19" s="46" t="s">
@@ -7640,7 +8018,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
       <c r="G20" s="24"/>
       <c r="H20" s="24"/>
       <c r="K20" s="46" t="s">
@@ -7650,7 +8032,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
       <c r="G21" s="24"/>
       <c r="H21" s="24"/>
       <c r="K21" s="46" t="s">
@@ -7660,7 +8046,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="24"/>
       <c r="H22" s="24"/>
       <c r="K22" s="47" t="s">
@@ -7670,61 +8056,61 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="24"/>
       <c r="H23" s="24"/>
       <c r="K23" s="17"/>
       <c r="L23" s="17"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="24"/>
       <c r="H24" s="24"/>
       <c r="K24" s="24"/>
       <c r="L24" s="24"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="18"/>
       <c r="H25" s="18"/>
       <c r="K25" s="18"/>
       <c r="L25" s="18"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="18"/>
       <c r="H26" s="18"/>
       <c r="K26" s="18"/>
       <c r="L26" s="18"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="18"/>
       <c r="H27" s="18"/>
       <c r="K27" s="18"/>
       <c r="L27" s="18"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="18"/>
       <c r="H28" s="18"/>
       <c r="K28" s="18"/>
       <c r="L28" s="18"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="18"/>
       <c r="H29" s="18"/>
       <c r="K29" s="18"/>
       <c r="L29" s="18"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="18"/>
       <c r="H30" s="18"/>
       <c r="K30" s="18"/>
       <c r="L30" s="18"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="18"/>
       <c r="H31" s="18"/>
       <c r="K31" s="18"/>
       <c r="L31" s="18"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="18"/>
       <c r="H32" s="18"/>
       <c r="K32" s="18"/>
